--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -3748,7 +3748,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-01</t>
+          <t>Generado el 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-02</t>
+          <t>Generado el 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
     </row>
@@ -12356,12 +12356,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -12446,12 +12446,12 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido contra el texto (una firma)</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -1027,7 +1027,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
     </row>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
     </row>
@@ -14557,7 +14557,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
     </row>
@@ -14599,7 +14599,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>consenso</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-14</t>
+          <t>Generado el 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -1241,12 +1241,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>acuerdo</t>
+          <t>corregido por consenso contra el texto</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,9 @@
     </font>
     <font>
       <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <sz val="10"/>
     </font>
     <font>
@@ -89,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -102,9 +105,19 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,7 +512,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anexo del material suplementario.</t>
+          <t>De dónde salió cada casilla de la extracción adjudicada (S14): el mismo cuadro, una fila por brazo y una columna por variable, con la etiqueta de procedencia en lugar del valor.</t>
         </is>
       </c>
     </row>
@@ -514,7 +527,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2.6 y tabla 5, cuyo «con doble lectura» cuenta las casillas con acuerdo, adjudicadas o corregidas con dos firmas. Cada etiqueta se explica abajo.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
@@ -822,14 +839,136 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
+          <t>Qué significa cada etiqueta</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>acuerdo (2026 casillas)</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Los dos revisores escribieron el mismo valor, una vez normalizado el vocabulario.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>adjudicada por los dos (13 casillas)</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Los dos revisores discreparon; el valor es el del registro de adjudicación (extraction_conflicts.csv), que anota como responsables a los dos. Solo estas constan como consenso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>adjudicada por uno (D.V.) (278 casillas)</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Los dos revisores discreparon; el valor es el del registro de adjudicación, que anota un único responsable: D.V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>adjudicada por uno (N.T.) (229 casillas)</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Los dos revisores discreparon; el valor es el del registro de adjudicación, que anota un único responsable: N.T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>corregido por consenso contra el texto (56 casillas)</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Casilla ya cerrada que una corrección posterior, con su cita literal y la firma de los dos autores, cambió contra el texto completo (correcciones_tras_texto_completo.csv). Las correcciones de modalidad las propuso el modelo de lenguaje tras leer los textos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>corregido contra el texto (una firma) (10 casillas)</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Lo mismo, con la firma de un solo autor; no cuenta como doble lectura. Entre ellas están las casillas del tercer paciente de EST-121, que extrajo el modelo de lenguaje y firmó solo D.V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>sin segunda lectura (156 casillas)</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Solo un revisor rellenó la casilla; no cuenta como doble lectura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>ABIERTO (2 casillas)</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Los dos discreparon y el desacuerdo no está adjudicado; la casilla sale vacía en S14. Así queda también un desacuerdo que se cerró por una regla mecánica, sin firma conjunta: su valor no lo firmó nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>vacio (2 casillas)</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Ninguno de los dos rellenó la casilla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Una casilla adjudicada que después se corrigió contra el texto lleva la etiqueta de la corrección; por eso las casillas «adjudicada» son menos que los desacuerdos adjudicados del registro. Que el registro anote un único responsable dice quién firmó, no cuántos leyeron: la casilla la leyeron los dos, y por eso discreparon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -873,117 +1012,117 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>adverse_event_n</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>clinical_success_definition</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>clinical_success_n</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>¿Cumple criterio DTR?</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>extraction_citation</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>Estado de la extracción</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>geographic_source</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>incomplete_reason</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>journal_tier</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>los_days</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>microbio_eradication_n</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="12" t="inlineStr">
         <is>
           <t>¿Fago solo o con antibiótico?</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" s="12" t="inlineStr">
         <is>
           <t>mortality_n</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>Pacientes en el brazo</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="Q1" s="12" t="inlineStr">
         <is>
           <t>¿Solo P. aeruginosa o mixto?</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="R1" s="12" t="inlineStr">
         <is>
           <t>publication_year</t>
         </is>
       </c>
-      <c r="S1" s="8" t="inlineStr">
+      <c r="S1" s="12" t="inlineStr">
         <is>
           <t>Clase de resistencia</t>
         </is>
       </c>
-      <c r="T1" s="8" t="inlineStr">
+      <c r="T1" s="12" t="inlineStr">
         <is>
           <t>De dónde sale la clase</t>
         </is>
       </c>
-      <c r="U1" s="8" t="inlineStr">
+      <c r="U1" s="12" t="inlineStr">
         <is>
           <t>resistance_emergence_n</t>
         </is>
       </c>
-      <c r="V1" s="8" t="inlineStr">
+      <c r="V1" s="12" t="inlineStr">
         <is>
           <t>Vía de administración</t>
         </is>
       </c>
-      <c r="W1" s="8" t="inlineStr">
+      <c r="W1" s="12" t="inlineStr">
         <is>
           <t>Diseño del estudio</t>
         </is>
@@ -1007,7 +1146,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1027,7 +1166,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1052,7 +1191,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1097,7 +1236,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1124,7 +1263,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1134,7 +1273,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1169,7 +1308,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1179,7 +1318,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1214,7 +1353,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1236,7 +1375,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1266,7 +1405,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1291,17 +1430,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1331,7 +1470,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1353,7 +1492,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1363,7 +1502,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1403,7 +1542,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1413,7 +1552,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1480,7 +1619,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1520,7 +1659,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1535,7 +1674,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1587,7 +1726,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1597,7 +1736,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1637,7 +1776,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1647,12 +1786,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1714,7 +1853,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1754,12 +1893,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1799,7 +1938,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1826,12 +1965,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1851,7 +1990,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1871,7 +2010,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1886,7 +2025,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1921,7 +2060,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -1943,7 +2082,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1953,7 +2092,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1968,7 +2107,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2060,7 +2199,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2085,7 +2224,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2105,12 +2244,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2150,7 +2289,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2177,7 +2316,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2217,12 +2356,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2267,7 +2406,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2294,7 +2433,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2339,7 +2478,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2379,7 +2518,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2411,7 +2550,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2431,12 +2570,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2456,7 +2595,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2471,7 +2610,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2645,7 +2784,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2690,7 +2829,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2735,7 +2874,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2762,7 +2901,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2797,7 +2936,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2807,12 +2946,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2879,7 +3018,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2889,7 +3028,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2899,12 +3038,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2969,7 +3108,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2991,17 +3130,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3041,12 +3180,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3081,7 +3220,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3113,7 +3252,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3123,7 +3262,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3133,7 +3272,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3230,7 +3369,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3255,7 +3394,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3315,7 +3454,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3347,17 +3486,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3372,7 +3511,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3392,7 +3531,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3432,17 +3571,17 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3603,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3474,7 +3613,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3489,7 +3628,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3509,12 +3648,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3549,17 +3688,17 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -3576,22 +3715,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3601,12 +3740,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3631,7 +3770,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3641,7 +3780,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3651,7 +3790,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3671,12 +3810,12 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3837,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3718,7 +3857,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3743,7 +3882,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3815,7 +3954,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3825,7 +3964,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3835,12 +3974,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3870,12 +4009,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3885,7 +4024,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3905,12 +4044,12 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
     </row>
@@ -3927,17 +4066,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3952,12 +4091,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3982,7 +4121,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4044,12 +4183,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4074,7 +4213,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4104,7 +4243,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4144,7 +4283,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4305,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4261,7 +4400,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -4278,12 +4417,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4293,7 +4432,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4303,7 +4442,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4333,7 +4472,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4378,7 +4517,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4534,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4420,7 +4559,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4450,17 +4589,17 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4517,7 +4656,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4542,7 +4681,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4612,7 +4751,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4773,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4679,7 +4818,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4694,7 +4833,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4985,7 +5124,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4995,7 +5134,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5005,12 +5144,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5020,7 +5159,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -5040,7 +5179,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5080,7 +5219,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5475,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5361,7 +5500,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5381,7 +5520,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5396,7 +5535,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -5426,12 +5565,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5592,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5493,7 +5632,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5538,7 +5677,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -5570,7 +5709,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5615,7 +5754,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5660,12 +5799,12 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5943,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5894,12 +6033,12 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -5916,12 +6055,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5931,7 +6070,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5946,7 +6085,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5971,7 +6110,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -6033,17 +6172,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6058,12 +6197,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6093,7 +6232,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6128,7 +6267,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6272,7 +6411,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6367,7 +6506,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6528,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6424,7 +6563,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -6484,7 +6623,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6645,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6541,7 +6680,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -6551,7 +6690,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6601,7 +6740,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -6618,22 +6757,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6643,12 +6782,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6678,7 +6817,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6693,7 +6832,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -6735,12 +6874,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6760,7 +6899,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6775,7 +6914,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -6785,7 +6924,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6795,7 +6934,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6830,12 +6969,12 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6996,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6867,7 +7006,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6902,7 +7041,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6942,7 +7081,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -7091,7 +7230,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7136,7 +7275,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7186,7 +7325,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7464,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7335,7 +7474,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7345,7 +7484,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7365,7 +7504,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -7375,7 +7514,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -7385,7 +7524,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -7410,7 +7549,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -7420,7 +7559,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7581,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7487,7 +7626,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -7532,12 +7671,12 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7698,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7594,7 +7733,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -7604,7 +7743,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -7654,7 +7793,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7810,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7696,7 +7835,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7726,7 +7865,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -7736,7 +7875,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -7766,12 +7905,12 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
     </row>
@@ -7788,22 +7927,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -7813,12 +7952,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7853,7 +7992,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -7863,7 +8002,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -7888,7 +8027,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -7910,7 +8049,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7935,7 +8074,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7965,12 +8104,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -8027,7 +8166,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -8062,7 +8201,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -8490,12 +8629,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -8505,7 +8644,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -8530,7 +8669,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -8550,7 +8689,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8590,7 +8729,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -8607,12 +8746,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8632,12 +8771,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8662,7 +8801,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -8707,7 +8846,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8868,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8739,7 +8878,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -8749,7 +8888,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8764,7 +8903,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -8784,7 +8923,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8814,7 +8953,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -8841,12 +8980,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8856,7 +8995,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -8866,7 +9005,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8891,7 +9030,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -8901,7 +9040,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8936,12 +9075,12 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -8958,17 +9097,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8988,7 +9127,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9018,7 +9157,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9053,7 +9192,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -9080,7 +9219,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -9090,7 +9229,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9105,7 +9244,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9115,7 +9254,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -9135,7 +9274,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9175,7 +9314,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9453,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -9339,7 +9478,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9349,7 +9488,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -9374,7 +9513,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -9399,17 +9538,17 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -9660,12 +9799,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -9720,7 +9859,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9782,12 +9921,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9817,27 +9956,27 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9899,7 +10038,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9934,7 +10073,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -9944,7 +10083,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -9989,7 +10128,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -10016,12 +10155,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -10051,12 +10190,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -10101,7 +10240,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -10111,7 +10250,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10506,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -10387,7 +10526,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10402,7 +10541,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -10412,7 +10551,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -10457,7 +10596,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -10479,12 +10618,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -10519,7 +10658,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -10529,7 +10668,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10596,12 +10735,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -10611,7 +10750,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -10621,7 +10760,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10651,17 +10790,17 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -10691,12 +10830,12 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -10713,12 +10852,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -10728,7 +10867,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -10738,12 +10877,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10813,7 +10952,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
     </row>
@@ -10835,12 +10974,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -10875,7 +11014,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -10885,12 +11024,12 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -11064,17 +11203,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -11094,7 +11233,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11104,7 +11243,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -11124,12 +11263,12 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -11139,7 +11278,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -11159,12 +11298,12 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11325,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -11211,7 +11350,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11221,7 +11360,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -11231,7 +11370,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -11883,12 +12022,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -11908,12 +12047,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11938,7 +12077,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -11948,7 +12087,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -11958,7 +12097,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -11978,12 +12117,12 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
     </row>
@@ -12117,17 +12256,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -12182,7 +12321,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -12212,12 +12351,12 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12373,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -12264,7 +12403,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12284,7 +12423,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -12294,12 +12433,12 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -12309,7 +12448,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -12590,7 +12729,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -12635,7 +12774,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -12702,12 +12841,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -12732,7 +12871,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12742,12 +12881,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -12767,7 +12906,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -12824,7 +12963,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -12849,7 +12988,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12869,12 +13008,12 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -12941,7 +13080,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12986,12 +13125,12 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -13058,7 +13197,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -13068,7 +13207,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -13083,7 +13222,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -13093,7 +13232,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -13103,17 +13242,17 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -13128,7 +13267,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -13143,12 +13282,12 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
@@ -13175,12 +13314,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -13215,7 +13354,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -13230,12 +13369,12 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -13287,12 +13426,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -13312,12 +13451,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -13342,7 +13481,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -13352,7 +13491,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -13362,7 +13501,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -13382,12 +13521,12 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13548,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -13434,7 +13573,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13444,7 +13583,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -13454,12 +13593,12 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -13499,12 +13638,12 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -13521,17 +13660,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -13561,7 +13700,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -13760,7 +13899,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -13785,7 +13924,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13855,7 +13994,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -13989,12 +14128,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -14039,22 +14178,22 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -14089,7 +14228,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -14106,12 +14245,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -14131,12 +14270,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -14161,17 +14300,17 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -14201,12 +14340,12 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
     </row>
@@ -14228,7 +14367,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -14345,12 +14484,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -14380,7 +14519,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -14390,7 +14529,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -14405,7 +14544,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -14435,7 +14574,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
@@ -14457,12 +14596,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -14482,12 +14621,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14512,7 +14651,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -14522,7 +14661,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -14532,7 +14671,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -14552,12 +14691,12 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
     </row>
@@ -14574,12 +14713,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -14599,12 +14738,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14629,7 +14768,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -14639,7 +14778,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -14649,7 +14788,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -14669,12 +14808,12 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14835,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -14786,7 +14925,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -14813,17 +14952,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -14838,7 +14977,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -14858,7 +14997,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -14883,7 +15022,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -14898,12 +15037,12 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -15164,7 +15303,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -15189,7 +15328,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -15199,7 +15338,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -15219,7 +15358,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -15259,7 +15398,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
     </row>
@@ -15281,12 +15420,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -15321,12 +15460,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -15371,12 +15510,12 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
     </row>
@@ -15749,7 +15888,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -15774,7 +15913,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15799,7 +15938,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -15839,7 +15978,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
@@ -16217,7 +16356,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -16262,7 +16401,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -16329,12 +16468,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -16354,12 +16493,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16384,7 +16523,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -16394,7 +16533,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -16404,7 +16543,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (D.V.)</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -16424,12 +16563,12 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por uno (N.T.)</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>adjudicada por los dos</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -92,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -103,21 +107,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -485,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -529,446 +536,453 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Sección 2.6 y tabla 5, cuyo «con doble lectura» cuenta las casillas con acuerdo, adjudicadas o corregidas con dos firmas. Cada etiqueta se explica abajo.</t>
+          <t>Sección 2.6 y tabla 5, cuyo «con doble lectura» cuenta las casillas con acuerdo o adjudicadas, por uno o por los dos; las corregidas contra el texto no cuentan, tampoco las de dos firmas. Cada etiqueta se explica abajo.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas; allí la tabla 5 (desenlaces) es la Tabla 4.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>132 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: arm_id</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>adverse_event_n</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: adverse_event_n</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>clinical_success_definition</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: clinical_success_definition</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>clinical_success_n</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: clinical_success_n</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>¿Cumple criterio DTR?</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: dtr_status</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>extraction_citation</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: extraction_citation</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Estado de la extracción</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: extraction_status</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>geographic_source</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: geographic_source</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>incomplete_reason</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: incomplete_reason</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>journal_tier</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: journal_tier</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>los_days</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>columna interna: los_days</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>microbio_eradication_n</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>columna interna: microbio_eradication_n</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>¿Fago solo o con antibiótico?</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>columna interna: modality</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>mortality_n</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>columna interna: mortality_n</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Pacientes en el brazo</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>columna interna: n_arm</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>¿Solo P. aeruginosa o mixto?</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>columna interna: pathogen_scope</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>publication_year</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>columna interna: publication_year</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Clase de resistencia</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>columna interna: resistance_class</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>De dónde sale la clase</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>columna interna: resistance_class_source</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>resistance_emergence_n</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>columna interna: resistance_emergence_n</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Vía de administración</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>columna interna: route</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Diseño del estudio</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_design</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Qué significa cada etiqueta</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
+          <t>Qué significa cada etiqueta</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
           <t>acuerdo (2026 casillas)</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Los dos revisores escribieron el mismo valor, una vez normalizado el vocabulario.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>adjudicada por los dos (13 casillas)</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Los dos revisores discreparon; el valor es el del registro de adjudicación (extraction_conflicts.csv), que anota como responsables a los dos. Solo estas constan como consenso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Los dos revisores discreparon; el valor es el del registro de adjudicación (extraction_conflicts.csv), que anota como responsables a los dos. Entre las casillas adjudicadas, solo estas constan como consenso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>adjudicada por uno (D.V.) (278 casillas)</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Los dos revisores discreparon; el valor es el del registro de adjudicación, que anota un único responsable: D.V.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>adjudicada por uno (N.T.) (229 casillas)</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Los dos revisores discreparon; el valor es el del registro de adjudicación, que anota un único responsable: N.T.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>corregido por consenso contra el texto (56 casillas)</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Casilla ya cerrada que una corrección posterior, con su cita literal y la firma de los dos autores, cambió contra el texto completo (correcciones_tras_texto_completo.csv). Las correcciones de modalidad las propuso el modelo de lenguaje tras leer los textos.</t>
-        </is>
-      </c>
-    </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>corregido contra el texto (dos firmas) (56 casillas)</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Casilla ya cerrada que una corrección posterior, con su cita literal y la firma de los dos autores, cambió contra el texto completo (correcciones_tras_texto_completo.csv). Las correcciones de modalidad las propuso el modelo de lenguaje tras leer los textos. No cuenta como doble lectura en la tabla 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>corregido contra el texto (una firma) (10 casillas)</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Lo mismo, con la firma de un solo autor; no cuenta como doble lectura. Entre ellas están las casillas del tercer paciente de EST-121, que extrajo el modelo de lenguaje y firmó solo D.V.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>sin segunda lectura (156 casillas)</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Solo un revisor rellenó la casilla; no cuenta como doble lectura.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>ABIERTO (2 casillas)</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Los dos discreparon y el desacuerdo no está adjudicado; la casilla sale vacía en S14. Así queda también un desacuerdo que se cerró por una regla mecánica, sin firma conjunta: su valor no lo firmó nadie.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>vacio (2 casillas)</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Ninguno de los dos rellenó la casilla.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="9" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Una casilla adjudicada que después se corrigió contra el texto lleva la etiqueta de la corrección; por eso las casillas «adjudicada» son menos que los desacuerdos adjudicados del registro. Que el registro anote un único responsable dice quién firmó, no cuántos leyeron: la casilla la leyeron los dos, y por eso discreparon.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>Generado el 2026-10-12</t>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1012,117 +1026,117 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>adverse_event_n</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>clinical_success_definition</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>clinical_success_n</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>¿Cumple criterio DTR?</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>extraction_citation</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Estado de la extracción</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>geographic_source</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>incomplete_reason</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>journal_tier</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>los_days</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>microbio_eradication_n</t>
         </is>
       </c>
-      <c r="N1" s="12" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>¿Fago solo o con antibiótico?</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="13" t="inlineStr">
         <is>
           <t>mortality_n</t>
         </is>
       </c>
-      <c r="P1" s="12" t="inlineStr">
+      <c r="P1" s="13" t="inlineStr">
         <is>
           <t>Pacientes en el brazo</t>
         </is>
       </c>
-      <c r="Q1" s="12" t="inlineStr">
+      <c r="Q1" s="13" t="inlineStr">
         <is>
           <t>¿Solo P. aeruginosa o mixto?</t>
         </is>
       </c>
-      <c r="R1" s="12" t="inlineStr">
+      <c r="R1" s="13" t="inlineStr">
         <is>
           <t>publication_year</t>
         </is>
       </c>
-      <c r="S1" s="12" t="inlineStr">
+      <c r="S1" s="13" t="inlineStr">
         <is>
           <t>Clase de resistencia</t>
         </is>
       </c>
-      <c r="T1" s="12" t="inlineStr">
+      <c r="T1" s="13" t="inlineStr">
         <is>
           <t>De dónde sale la clase</t>
         </is>
       </c>
-      <c r="U1" s="12" t="inlineStr">
+      <c r="U1" s="13" t="inlineStr">
         <is>
           <t>resistance_emergence_n</t>
         </is>
       </c>
-      <c r="V1" s="12" t="inlineStr">
+      <c r="V1" s="13" t="inlineStr">
         <is>
           <t>Vía de administración</t>
         </is>
       </c>
-      <c r="W1" s="12" t="inlineStr">
+      <c r="W1" s="13" t="inlineStr">
         <is>
           <t>Diseño del estudio</t>
         </is>
@@ -1343,7 +1357,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1380,12 +1394,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1497,7 +1511,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1614,7 +1628,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1731,7 +1745,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1848,7 +1862,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2045,7 +2059,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -2396,7 +2410,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2794,7 +2808,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2911,7 +2925,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3215,7 +3229,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3444,12 +3458,12 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3887,7 +3901,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3917,7 +3931,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4126,12 +4140,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4315,7 +4329,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4385,7 +4399,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4666,7 +4680,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5525,7 +5539,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -5953,7 +5967,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6135,12 +6149,12 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6257,7 +6271,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6421,7 +6435,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6486,7 +6500,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6538,7 +6552,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6603,12 +6617,12 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6720,7 +6734,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -7305,7 +7319,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -7656,7 +7670,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7708,7 +7722,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -7778,7 +7792,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8059,7 +8073,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8129,7 +8143,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -9214,7 +9228,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9854,7 +9868,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -9884,7 +9898,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10113,12 +10127,12 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -10586,7 +10600,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -10633,7 +10647,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -10703,7 +10717,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -11218,7 +11232,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -11283,7 +11297,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -11400,7 +11414,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -12428,7 +12442,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -12739,7 +12753,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -12804,12 +12818,12 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -14494,7 +14508,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -14564,7 +14578,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -15353,7 +15367,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>corregido por consenso contra el texto</t>
+          <t>corregido contra el texto (dos firmas)</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -982,7 +982,7 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -982,7 +982,7 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -519,7 +519,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>De dónde salió cada casilla de la extracción adjudicada (S14): el mismo cuadro, una fila por brazo y una columna por variable, con la etiqueta de procedencia en lugar del valor.</t>
+          <t>De dónde salió cada casilla de la extracción adjudicada (S14): el mismo cuadro, una fila por brazo y una columna por variable, con la etiqueta de procedencia en lugar del valor. De sus 132 filas, 59 son brazos de estudios que salieron después del cribado (S16); la sección y las tablas que se citan abajo cuentan solo los 73 brazos de los estudios que siguen en el corpus, y los recuentos de etiquetas de esta hoja incluyen todas las filas.</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>adverse_event_n</t>
+          <t>Eventos adversos (nº)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>clinical_success_definition</t>
+          <t>¿Cómo define el AUTOR el éxito clínico?</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>clinical_success_n</t>
+          <t>Éxito clínico (nº pacientes)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>extraction_citation</t>
+          <t>¿Dónde viste estos datos?</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>geographic_source</t>
+          <t>País del estudio</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>incomplete_reason</t>
+          <t>Si algo quedó incompleto, ¿por qué?</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>journal_tier</t>
+          <t>Nivel de la revista</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>los_days</t>
+          <t>Estancia hospitalaria (días)</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>microbio_eradication_n</t>
+          <t>Erradicación microbiológica (nº)</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>mortality_n</t>
+          <t>Fallecidos (nº)</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>publication_year</t>
+          <t>Año de publicación</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>resistance_emergence_n</t>
+          <t>Aparición de resistencia al fago (nº)</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Casilla ya cerrada que una corrección posterior, con su cita literal y la firma de los dos autores, cambió contra el texto completo (correcciones_tras_texto_completo.csv). Las correcciones de modalidad las propuso el modelo de lenguaje tras leer los textos. No cuenta como doble lectura en la tabla 5.</t>
+          <t>Casilla ya cerrada que una corrección posterior, con su cita literal y la firma de los dos autores, cambió contra el texto completo (correcciones_tras_texto_completo.csv). Las correcciones de modalidad las propuso el modelo de lenguaje tras leer los textos. 35 de estas casillas («Clase de resistencia», «De dónde sale la clase» y «¿Cumple criterio DTR?») son correcciones de la relectura del 30 de septiembre de 2026: los dos autores firmaron su conclusión en texto libre, y el valor que entró en la casilla lo derivó de ese texto el modelo de lenguaje (ingest_lectura_firmada.py). Lo firmado es la conclusión, no el valor. No cuenta como doble lectura en la tabla 5.</t>
         </is>
       </c>
     </row>
@@ -1038,17 +1038,17 @@
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
-          <t>adverse_event_n</t>
+          <t>Eventos adversos (nº)</t>
         </is>
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>clinical_success_definition</t>
+          <t>¿Cómo define el AUTOR el éxito clínico?</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>clinical_success_n</t>
+          <t>Éxito clínico (nº pacientes)</t>
         </is>
       </c>
       <c r="F1" s="13" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="G1" s="13" t="inlineStr">
         <is>
-          <t>extraction_citation</t>
+          <t>¿Dónde viste estos datos?</t>
         </is>
       </c>
       <c r="H1" s="13" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="I1" s="13" t="inlineStr">
         <is>
-          <t>geographic_source</t>
+          <t>País del estudio</t>
         </is>
       </c>
       <c r="J1" s="13" t="inlineStr">
         <is>
-          <t>incomplete_reason</t>
+          <t>Si algo quedó incompleto, ¿por qué?</t>
         </is>
       </c>
       <c r="K1" s="13" t="inlineStr">
         <is>
-          <t>journal_tier</t>
+          <t>Nivel de la revista</t>
         </is>
       </c>
       <c r="L1" s="13" t="inlineStr">
         <is>
-          <t>los_days</t>
+          <t>Estancia hospitalaria (días)</t>
         </is>
       </c>
       <c r="M1" s="13" t="inlineStr">
         <is>
-          <t>microbio_eradication_n</t>
+          <t>Erradicación microbiológica (nº)</t>
         </is>
       </c>
       <c r="N1" s="13" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="O1" s="13" t="inlineStr">
         <is>
-          <t>mortality_n</t>
+          <t>Fallecidos (nº)</t>
         </is>
       </c>
       <c r="P1" s="13" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="R1" s="13" t="inlineStr">
         <is>
-          <t>publication_year</t>
+          <t>Año de publicación</t>
         </is>
       </c>
       <c r="S1" s="13" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="U1" s="13" t="inlineStr">
         <is>
-          <t>resistance_emergence_n</t>
+          <t>Aparición de resistencia al fago (nº)</t>
         </is>
       </c>
       <c r="V1" s="13" t="inlineStr">

--- a/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
+++ b/verificables revisión sistemática/S15_procedencia_de_cada_casilla.xlsx
@@ -982,7 +982,7 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
